--- a/employee_surveys/024_pulse_survey--employee_surveys.xlsx
+++ b/employee_surveys/024_pulse_survey--employee_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -845,7 +845,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>very_unhappy</t>
+          <t>very unhappy</t>
         </is>
       </c>
     </row>
@@ -913,7 +913,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>very_happy</t>
+          <t>very happy</t>
         </is>
       </c>
     </row>
@@ -947,7 +947,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>somewhat_engaged</t>
+          <t>somewhat engaged</t>
         </is>
       </c>
     </row>
@@ -981,7 +981,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>somewhat_disengaged</t>
+          <t>somewhat disengaged</t>
         </is>
       </c>
     </row>
@@ -1049,7 +1049,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>very_fair</t>
+          <t>very fair</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>extremely_fair</t>
+          <t>extremely fair</t>
         </is>
       </c>
     </row>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>very_unfair</t>
+          <t>very unfair</t>
         </is>
       </c>
     </row>
@@ -1202,7 +1202,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>very_fair</t>
+          <t>very fair</t>
         </is>
       </c>
     </row>
@@ -1219,7 +1219,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>extremely_fair</t>
+          <t>extremely fair</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>very_unfair</t>
+          <t>very unfair</t>
         </is>
       </c>
     </row>
@@ -1338,7 +1338,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>work_life_balance</t>
+          <t>work life balance</t>
         </is>
       </c>
     </row>
@@ -1355,7 +1355,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>work_life_balance_score</t>
+          <t>work life balance score</t>
         </is>
       </c>
     </row>
@@ -1372,7 +1372,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>health_and_wellness</t>
+          <t>health and wellness</t>
         </is>
       </c>
     </row>
@@ -1389,7 +1389,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>time_off</t>
+          <t>time off</t>
         </is>
       </c>
     </row>
